--- a/data.mn/public/datasets/health-facilities-by-aimag.xlsx
+++ b/data.mn/public/datasets/health-facilities-by-aimag.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,18 +418,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Aimag</t>
+          <t>aimag</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>facilities_count</t>
         </is>
       </c>
     </row>
@@ -646,6 +647,256 @@
       <c r="A23" t="inlineStr">
         <is>
           <t>Govisumber</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>аймаг</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>байгууллагын_тоо</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Улаанбаатар</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Дархан-Уул</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Орхон</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Хөвсгөл</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Өвөрхангай</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Баян-Өлгий</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Баянхонгор</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Увс</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Өмнөговь</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ховд</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Дорноговь</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Архангай</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Хэнтий</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Говь-Алтай</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Сэлэнгэ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Дорнод</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Завхан</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Төв</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Дундговь</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Булган</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Сүхбаатар</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Говьсүмбэр</t>
         </is>
       </c>
       <c r="B23" t="n">
